--- a/data/external_sources/CSIRO_GenCost_2025.xlsx
+++ b/data/external_sources/CSIRO_GenCost_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dcceew2-my.sharepoint.com/personal/markus_mannheim_dcceew_gov_au/Documents/NEM Review (local)/Data analysis/Contract modelling/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dcceew2-my.sharepoint.com/personal/markus_mannheim_dcceew_gov_au/Documents/NEM Review (local)/Data analysis/Contract modelling/data/external_sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{B2E12E12-94AF-4A6D-9614-E98F40A6F6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FDEF5FD-F1CB-4FB6-A47F-E1613A0EBF3F}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B2E12E12-94AF-4A6D-9614-E98F40A6F6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E6C50B1-6F72-4662-A2AA-36D4547A1230}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1650" yWindow="1545" windowWidth="14400" windowHeight="8175" firstSheet="1" activeTab="8" xr2:uid="{F5285A18-784A-4AE7-87A8-FACFAD010027}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{F5285A18-784A-4AE7-87A8-FACFAD010027}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="11" r:id="rId1"/>
@@ -452,7 +452,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
@@ -652,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -853,18 +854,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1646,9 +1648,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB861386-0F0A-44C9-A36E-E19810534D32}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>116</v>
       </c>
@@ -1665,14 +1667,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2E1568-1D42-42A9-AAC0-ED26E064CFE2}">
   <dimension ref="B2:X37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="28.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:24" ht="36" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="29" t="s">
         <v>0</v>
@@ -1741,7 +1743,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -1810,7 +1812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>2024</v>
       </c>
@@ -1881,7 +1883,7 @@
         <v>8984</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="21">
         <v>2025</v>
       </c>
@@ -1952,7 +1954,7 @@
         <v>8858</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="20">
         <v>2026</v>
       </c>
@@ -2023,7 +2025,7 @@
         <v>8738</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="21">
         <v>2027</v>
       </c>
@@ -2094,7 +2096,7 @@
         <v>8667</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="20">
         <v>2028</v>
       </c>
@@ -2165,7 +2167,7 @@
         <v>8656</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <v>2029</v>
       </c>
@@ -2236,7 +2238,7 @@
         <v>8694</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="20">
         <v>2030</v>
       </c>
@@ -2307,7 +2309,7 @@
         <v>8736</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <v>2031</v>
       </c>
@@ -2378,7 +2380,7 @@
         <v>8778</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="20">
         <v>2032</v>
       </c>
@@ -2449,7 +2451,7 @@
         <v>8815</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="21">
         <v>2033</v>
       </c>
@@ -2520,7 +2522,7 @@
         <v>8851</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="20">
         <v>2034</v>
       </c>
@@ -2591,7 +2593,7 @@
         <v>8886</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <v>2035</v>
       </c>
@@ -2662,7 +2664,7 @@
         <v>8922</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="20">
         <v>2036</v>
       </c>
@@ -2733,7 +2735,7 @@
         <v>8958</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <v>2037</v>
       </c>
@@ -2804,7 +2806,7 @@
         <v>8994</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="20">
         <v>2038</v>
       </c>
@@ -2875,7 +2877,7 @@
         <v>9031</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="21">
         <v>2039</v>
       </c>
@@ -2946,7 +2948,7 @@
         <v>9068</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="20">
         <v>2040</v>
       </c>
@@ -3017,7 +3019,7 @@
         <v>9102</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="21">
         <v>2041</v>
       </c>
@@ -3088,7 +3090,7 @@
         <v>9132</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="20">
         <v>2042</v>
       </c>
@@ -3159,7 +3161,7 @@
         <v>9158</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <v>2043</v>
       </c>
@@ -3230,7 +3232,7 @@
         <v>9184</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="20">
         <v>2044</v>
       </c>
@@ -3301,7 +3303,7 @@
         <v>9210</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <v>2045</v>
       </c>
@@ -3372,7 +3374,7 @@
         <v>9236</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="20">
         <v>2046</v>
       </c>
@@ -3443,7 +3445,7 @@
         <v>9263</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="21">
         <v>2047</v>
       </c>
@@ -3514,7 +3516,7 @@
         <v>9289</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="20">
         <v>2048</v>
       </c>
@@ -3585,7 +3587,7 @@
         <v>9316</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="21">
         <v>2049</v>
       </c>
@@ -3656,7 +3658,7 @@
         <v>9343</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="20">
         <v>2050</v>
       </c>
@@ -3727,7 +3729,7 @@
         <v>9368</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="21">
         <v>2051</v>
       </c>
@@ -3798,7 +3800,7 @@
         <v>9391</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="20">
         <v>2052</v>
       </c>
@@ -3869,7 +3871,7 @@
         <v>9413</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="21">
         <v>2053</v>
       </c>
@@ -3940,7 +3942,7 @@
         <v>9435</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="20">
         <v>2054</v>
       </c>
@@ -4011,7 +4013,7 @@
         <v>9457</v>
       </c>
     </row>
-    <row r="37" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="42">
         <v>2055</v>
       </c>
@@ -4095,14 +4097,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F76FEDFE-762B-45A0-95AE-E0E01CD5002F}">
   <dimension ref="B2:X37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="28.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:24" ht="36" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="29" t="s">
         <v>0</v>
@@ -4171,7 +4173,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -4240,7 +4242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>2024</v>
       </c>
@@ -4311,7 +4313,7 @@
         <v>8984</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="21">
         <v>2025</v>
       </c>
@@ -4382,7 +4384,7 @@
         <v>8929</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="20">
         <v>2026</v>
       </c>
@@ -4453,7 +4455,7 @@
         <v>8881</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="21">
         <v>2027</v>
       </c>
@@ -4524,7 +4526,7 @@
         <v>8851</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="20">
         <v>2028</v>
       </c>
@@ -4595,7 +4597,7 @@
         <v>8854</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <v>2029</v>
       </c>
@@ -4666,7 +4668,7 @@
         <v>8876</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="20">
         <v>2030</v>
       </c>
@@ -4737,7 +4739,7 @@
         <v>8919</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <v>2031</v>
       </c>
@@ -4808,7 +4810,7 @@
         <v>8972</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="20">
         <v>2032</v>
       </c>
@@ -4879,7 +4881,7 @@
         <v>9035</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="21">
         <v>2033</v>
       </c>
@@ -4950,7 +4952,7 @@
         <v>9094</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="20">
         <v>2034</v>
       </c>
@@ -5021,7 +5023,7 @@
         <v>9154</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <v>2035</v>
       </c>
@@ -5092,7 +5094,7 @@
         <v>9214</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="20">
         <v>2036</v>
       </c>
@@ -5163,7 +5165,7 @@
         <v>9275</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <v>2037</v>
       </c>
@@ -5234,7 +5236,7 @@
         <v>9337</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="20">
         <v>2038</v>
       </c>
@@ -5305,7 +5307,7 @@
         <v>9400</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="21">
         <v>2039</v>
       </c>
@@ -5376,7 +5378,7 @@
         <v>9463</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="20">
         <v>2040</v>
       </c>
@@ -5447,7 +5449,7 @@
         <v>9524</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="21">
         <v>2041</v>
       </c>
@@ -5518,7 +5520,7 @@
         <v>9580</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="20">
         <v>2042</v>
       </c>
@@ -5589,7 +5591,7 @@
         <v>9633</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <v>2043</v>
       </c>
@@ -5660,7 +5662,7 @@
         <v>9687</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="20">
         <v>2044</v>
       </c>
@@ -5731,7 +5733,7 @@
         <v>9741</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <v>2045</v>
       </c>
@@ -5802,7 +5804,7 @@
         <v>9795</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="20">
         <v>2046</v>
       </c>
@@ -5873,7 +5875,7 @@
         <v>9850</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="21">
         <v>2047</v>
       </c>
@@ -5944,7 +5946,7 @@
         <v>9906</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="20">
         <v>2048</v>
       </c>
@@ -6015,7 +6017,7 @@
         <v>9962</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="21">
         <v>2049</v>
       </c>
@@ -6086,7 +6088,7 @@
         <v>10019</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="20">
         <v>2050</v>
       </c>
@@ -6157,7 +6159,7 @@
         <v>10074</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="21">
         <v>2051</v>
       </c>
@@ -6228,7 +6230,7 @@
         <v>10128</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="20">
         <v>2052</v>
       </c>
@@ -6299,7 +6301,7 @@
         <v>10180</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="21">
         <v>2053</v>
       </c>
@@ -6370,7 +6372,7 @@
         <v>10233</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="20">
         <v>2054</v>
       </c>
@@ -6441,7 +6443,7 @@
         <v>10287</v>
       </c>
     </row>
-    <row r="37" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="42">
         <v>2055</v>
       </c>
@@ -6525,14 +6527,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9020DB2-A90B-450A-BDD9-FACA538CA80B}">
   <dimension ref="B2:X37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="2:24" ht="28.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:24" ht="36" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="29" t="s">
         <v>0</v>
@@ -6601,7 +6603,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -6670,7 +6672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="20">
         <v>2024</v>
       </c>
@@ -6741,7 +6743,7 @@
         <v>8984</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="21">
         <v>2025</v>
       </c>
@@ -6812,7 +6814,7 @@
         <v>8924</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="20">
         <v>2026</v>
       </c>
@@ -6883,7 +6885,7 @@
         <v>8869</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="21">
         <v>2027</v>
       </c>
@@ -6954,7 +6956,7 @@
         <v>8823</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="20">
         <v>2028</v>
       </c>
@@ -7025,7 +7027,7 @@
         <v>8801</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="21">
         <v>2029</v>
       </c>
@@ -7096,7 +7098,7 @@
         <v>8792</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" s="20">
         <v>2030</v>
       </c>
@@ -7167,7 +7169,7 @@
         <v>8806</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" s="21">
         <v>2031</v>
       </c>
@@ -7238,7 +7240,7 @@
         <v>8836</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" s="20">
         <v>2032</v>
       </c>
@@ -7309,7 +7311,7 @@
         <v>8881</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" s="21">
         <v>2033</v>
       </c>
@@ -7380,7 +7382,7 @@
         <v>8924</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" s="20">
         <v>2034</v>
       </c>
@@ -7451,7 +7453,7 @@
         <v>8968</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="21">
         <v>2035</v>
       </c>
@@ -7522,7 +7524,7 @@
         <v>9012</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="20">
         <v>2036</v>
       </c>
@@ -7593,7 +7595,7 @@
         <v>9057</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="21">
         <v>2037</v>
       </c>
@@ -7664,7 +7666,7 @@
         <v>9102</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="20">
         <v>2038</v>
       </c>
@@ -7735,7 +7737,7 @@
         <v>9148</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="21">
         <v>2039</v>
       </c>
@@ -7806,7 +7808,7 @@
         <v>9195</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" s="20">
         <v>2040</v>
       </c>
@@ -7877,7 +7879,7 @@
         <v>9238</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="21">
         <v>2041</v>
       </c>
@@ -7948,7 +7950,7 @@
         <v>9277</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="20">
         <v>2042</v>
       </c>
@@ -8019,7 +8021,7 @@
         <v>9312</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" s="21">
         <v>2043</v>
       </c>
@@ -8090,7 +8092,7 @@
         <v>9348</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" s="20">
         <v>2044</v>
       </c>
@@ -8161,7 +8163,7 @@
         <v>9384</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="21">
         <v>2045</v>
       </c>
@@ -8232,7 +8234,7 @@
         <v>9420</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="20">
         <v>2046</v>
       </c>
@@ -8303,7 +8305,7 @@
         <v>9456</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="21">
         <v>2047</v>
       </c>
@@ -8374,7 +8376,7 @@
         <v>9493</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="20">
         <v>2048</v>
       </c>
@@ -8445,7 +8447,7 @@
         <v>9530</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="21">
         <v>2049</v>
       </c>
@@ -8516,7 +8518,7 @@
         <v>9567</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="20">
         <v>2050</v>
       </c>
@@ -8587,7 +8589,7 @@
         <v>9602</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="21">
         <v>2051</v>
       </c>
@@ -8658,7 +8660,7 @@
         <v>9636</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="20">
         <v>2052</v>
       </c>
@@ -8729,7 +8731,7 @@
         <v>9668</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="21">
         <v>2053</v>
       </c>
@@ -8800,7 +8802,7 @@
         <v>9701</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="20">
         <v>2054</v>
       </c>
@@ -8871,7 +8873,7 @@
         <v>9733</v>
       </c>
     </row>
-    <row r="37" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="42">
         <v>2055</v>
       </c>
@@ -8954,9 +8956,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAB4458A-E119-4B40-8368-16457BAFD692}">
   <dimension ref="B2:BK44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>28</v>
       </c>
@@ -8967,7 +8969,13 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:63" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="Y4" s="78">
+        <f>PMT(0.07,25,X11*4)</f>
+        <v>-145.19139513736621</v>
+      </c>
+    </row>
+    <row r="7" spans="2:63" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="68" t="s">
         <v>26</v>
@@ -9041,7 +9049,7 @@
       <c r="BJ7" s="68"/>
       <c r="BK7" s="68"/>
     </row>
-    <row r="8" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
       <c r="C8" s="24" t="s">
         <v>19</v>
@@ -9139,7 +9147,7 @@
       <c r="BJ8" s="7"/>
       <c r="BK8" s="7"/>
     </row>
-    <row r="9" spans="2:63" ht="21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:63" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="25" t="s">
         <v>79</v>
@@ -9309,7 +9317,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
       <c r="C10" s="23" t="s">
         <v>21</v>
@@ -9479,7 +9487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>2024</v>
       </c>
@@ -9652,7 +9660,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>2025</v>
       </c>
@@ -9828,7 +9836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>2026</v>
       </c>
@@ -10001,7 +10009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>2027</v>
       </c>
@@ -10177,7 +10185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>2028</v>
       </c>
@@ -10350,7 +10358,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>2029</v>
       </c>
@@ -10526,7 +10534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>2030</v>
       </c>
@@ -10699,7 +10707,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>2031</v>
       </c>
@@ -10875,7 +10883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>2032</v>
       </c>
@@ -11048,7 +11056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>2033</v>
       </c>
@@ -11224,7 +11232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>2034</v>
       </c>
@@ -11397,7 +11405,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>2035</v>
       </c>
@@ -11573,7 +11581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>2036</v>
       </c>
@@ -11746,7 +11754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>2037</v>
       </c>
@@ -11922,7 +11930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>2038</v>
       </c>
@@ -12095,7 +12103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>2039</v>
       </c>
@@ -12271,7 +12279,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>2040</v>
       </c>
@@ -12444,7 +12452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>2041</v>
       </c>
@@ -12620,7 +12628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>2042</v>
       </c>
@@ -12793,7 +12801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <v>2043</v>
       </c>
@@ -12969,7 +12977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>2044</v>
       </c>
@@ -13142,7 +13150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B32" s="5">
         <v>2045</v>
       </c>
@@ -13318,7 +13326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>2046</v>
       </c>
@@ -13491,7 +13499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>2047</v>
       </c>
@@ -13667,7 +13675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>2048</v>
       </c>
@@ -13840,7 +13848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>2049</v>
       </c>
@@ -14016,7 +14024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>2050</v>
       </c>
@@ -14189,7 +14197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <v>2051</v>
       </c>
@@ -14365,7 +14373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>2052</v>
       </c>
@@ -14541,7 +14549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B40" s="5">
         <v>2053</v>
       </c>
@@ -14717,7 +14725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>2054</v>
       </c>
@@ -14893,7 +14901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="45">
         <v>2055</v>
       </c>
@@ -15069,7 +15077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:63" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
         <v>83</v>
       </c>
@@ -15095,14 +15103,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C77FCA7F-0D6F-4780-9D9F-6F1A1FA60541}">
   <dimension ref="B2:U39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="69" t="s">
         <v>15</v>
@@ -15128,7 +15136,7 @@
       <c r="T5" s="69"/>
       <c r="U5" s="69"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
       <c r="C6" s="70" t="s">
         <v>79</v>
@@ -15162,7 +15170,7 @@
       <c r="T6" s="70"/>
       <c r="U6" s="70"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
       <c r="C7" s="53" t="s">
         <v>108</v>
@@ -15220,7 +15228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="21">
         <v>2024</v>
       </c>
@@ -15280,7 +15288,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="20">
         <v>2025</v>
       </c>
@@ -15340,7 +15348,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="21">
         <v>2026</v>
       </c>
@@ -15400,7 +15408,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="20">
         <v>2027</v>
       </c>
@@ -15460,7 +15468,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="21">
         <v>2028</v>
       </c>
@@ -15520,7 +15528,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="20">
         <v>2029</v>
       </c>
@@ -15580,7 +15588,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="21">
         <v>2030</v>
       </c>
@@ -15640,7 +15648,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="20">
         <v>2031</v>
       </c>
@@ -15700,7 +15708,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="21">
         <v>2032</v>
       </c>
@@ -15760,7 +15768,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="20">
         <v>2033</v>
       </c>
@@ -15820,7 +15828,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="21">
         <v>2034</v>
       </c>
@@ -15880,7 +15888,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="20">
         <v>2035</v>
       </c>
@@ -15940,7 +15948,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="21">
         <v>2036</v>
       </c>
@@ -16000,7 +16008,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="20">
         <v>2037</v>
       </c>
@@ -16060,7 +16068,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="21">
         <v>2038</v>
       </c>
@@ -16120,7 +16128,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="20">
         <v>2039</v>
       </c>
@@ -16180,7 +16188,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="21">
         <v>2040</v>
       </c>
@@ -16240,7 +16248,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="20">
         <v>2041</v>
       </c>
@@ -16300,7 +16308,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="21">
         <v>2042</v>
       </c>
@@ -16360,7 +16368,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="20">
         <v>2043</v>
       </c>
@@ -16420,7 +16428,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="21">
         <v>2044</v>
       </c>
@@ -16480,7 +16488,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="20">
         <v>2045</v>
       </c>
@@ -16540,7 +16548,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="21">
         <v>2046</v>
       </c>
@@ -16600,7 +16608,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="20">
         <v>2047</v>
       </c>
@@ -16660,7 +16668,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="21">
         <v>2048</v>
       </c>
@@ -16720,7 +16728,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="20">
         <v>2049</v>
       </c>
@@ -16780,7 +16788,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" s="21">
         <v>2050</v>
       </c>
@@ -16840,7 +16848,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B35" s="20">
         <v>2051</v>
       </c>
@@ -16900,7 +16908,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" s="21">
         <v>2052</v>
       </c>
@@ -16960,7 +16968,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B37" s="20">
         <v>2053</v>
       </c>
@@ -17020,7 +17028,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B38" s="21">
         <v>2054</v>
       </c>
@@ -17080,7 +17088,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="57">
         <v>2055</v>
       </c>
@@ -17162,20 +17170,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BB45DD-A5D5-4232-8035-659F50AA7A84}">
   <dimension ref="C3:U19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.1796875" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" customWidth="1"/>
-    <col min="12" max="12" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C6" s="8"/>
       <c r="D6" s="47" t="s">
         <v>21</v>
@@ -17200,7 +17208,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C7" s="7"/>
       <c r="D7" s="48" t="s">
         <v>73</v>
@@ -17257,7 +17265,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C8" s="49" t="s">
         <v>30</v>
       </c>
@@ -17316,7 +17324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C9" s="51" t="s">
         <v>32</v>
       </c>
@@ -17375,7 +17383,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C10" s="49" t="s">
         <v>33</v>
       </c>
@@ -17434,7 +17442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C11" s="51" t="s">
         <v>34</v>
       </c>
@@ -17493,7 +17501,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C12" s="49" t="s">
         <v>114</v>
       </c>
@@ -17552,7 +17560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C13" s="51" t="s">
         <v>101</v>
       </c>
@@ -17611,7 +17619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C14" s="49" t="s">
         <v>110</v>
       </c>
@@ -17670,7 +17678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C15" s="51" t="s">
         <v>92</v>
       </c>
@@ -17729,7 +17737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C16" s="49" t="s">
         <v>35</v>
       </c>
@@ -17788,7 +17796,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C17" s="51" t="s">
         <v>102</v>
       </c>
@@ -17847,7 +17855,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C18" s="49" t="s">
         <v>36</v>
       </c>
@@ -17906,7 +17914,7 @@
         <v>4140</v>
       </c>
     </row>
-    <row r="19" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="54" t="s">
         <v>37</v>
       </c>
@@ -17978,30 +17986,30 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CB6A7E-98E7-470E-8E31-B34111E61C87}">
   <dimension ref="B2:BT80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.7265625" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" customWidth="1"/>
-    <col min="12" max="12" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.81640625" customWidth="1"/>
-    <col min="14" max="14" width="9.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" customWidth="1"/>
     <col min="15" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.26953125" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.28515625" customWidth="1"/>
     <col min="18" max="18" width="4" customWidth="1"/>
-    <col min="36" max="36" width="31.26953125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>98</v>
       </c>
@@ -18012,7 +18020,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="4" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B4" s="8"/>
       <c r="C4" s="32" t="s">
         <v>39</v>
@@ -18046,7 +18054,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
         <v>44</v>
@@ -18131,7 +18139,7 @@
       <c r="BE5" s="18"/>
       <c r="BF5" s="18"/>
     </row>
-    <row r="6" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
       <c r="C6" s="1" t="s">
         <v>54</v>
@@ -18193,7 +18201,7 @@
       </c>
       <c r="AS6" s="8"/>
     </row>
-    <row r="7" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B7" s="16">
         <v>2024</v>
       </c>
@@ -18253,7 +18261,7 @@
       <c r="BR7" s="18"/>
       <c r="BS7" s="18"/>
     </row>
-    <row r="8" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="str">
         <f>'[1]Table data (2)'!A6</f>
         <v>Gas with CCS</v>
@@ -18401,7 +18409,7 @@
       <c r="BS8" s="18"/>
       <c r="BT8" s="18"/>
     </row>
-    <row r="9" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B9" s="30" t="str">
         <f>'[1]Table data (2)'!A7</f>
         <v>Gas combined cycle</v>
@@ -18547,7 +18555,7 @@
       <c r="BS9" s="18"/>
       <c r="BT9" s="18"/>
     </row>
-    <row r="10" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B10" s="30" t="str">
         <f>'[1]Table data (2)'!A8</f>
         <v>Gas open cycle (small)</v>
@@ -18693,7 +18701,7 @@
       <c r="BS10" s="18"/>
       <c r="BT10" s="18"/>
     </row>
-    <row r="11" spans="2:72" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:72" ht="18" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="str">
         <f>'[1]Table data (2)'!A9</f>
         <v>Gas open cycle (large)</v>
@@ -18736,6 +18744,10 @@
       </c>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
+      <c r="S11" s="78">
+        <f>PMT(0.07,C11,N11)</f>
+        <v>-112.41011886343087</v>
+      </c>
       <c r="U11" s="18">
         <f t="shared" si="0"/>
         <v>71.014489883073182</v>
@@ -18837,7 +18849,7 @@
       <c r="BS11" s="18"/>
       <c r="BT11" s="18"/>
     </row>
-    <row r="12" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B12" s="30" t="str">
         <f>'[1]Table data (2)'!A10</f>
         <v>Gas reciprocating</v>
@@ -18880,6 +18892,10 @@
       </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
+      <c r="S12" s="78">
+        <f>S11*0.4</f>
+        <v>-44.964047545372352</v>
+      </c>
       <c r="U12" s="18">
         <f t="shared" si="0"/>
         <v>104.57852967437687</v>
@@ -18985,7 +19001,7 @@
       <c r="BS12" s="18"/>
       <c r="BT12" s="18"/>
     </row>
-    <row r="13" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B13" s="30" t="str">
         <f>'[1]Table data (2)'!A11</f>
         <v>Hydrogen reciprocating</v>
@@ -19132,7 +19148,7 @@
       <c r="BS13" s="18"/>
       <c r="BT13" s="18"/>
     </row>
-    <row r="14" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="str">
         <f>'[1]Table data (2)'!A12</f>
         <v>Black coal with CCS</v>
@@ -19278,7 +19294,7 @@
       <c r="BS14" s="18"/>
       <c r="BT14" s="18"/>
     </row>
-    <row r="15" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B15" s="30" t="str">
         <f>'[1]Table data (2)'!A13</f>
         <v>Black coal</v>
@@ -19426,7 +19442,7 @@
       <c r="BS15" s="18"/>
       <c r="BT15" s="18"/>
     </row>
-    <row r="16" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B16" s="30" t="str">
         <f>'[1]Table data (2)'!A14</f>
         <v>Brown coal</v>
@@ -19572,7 +19588,7 @@
       <c r="BS16" s="18"/>
       <c r="BT16" s="18"/>
     </row>
-    <row r="17" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
         <v>105</v>
       </c>
@@ -19717,7 +19733,7 @@
       <c r="BS17" s="18"/>
       <c r="BT17" s="18"/>
     </row>
-    <row r="18" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B18" s="30" t="s">
         <v>106</v>
       </c>
@@ -19860,7 +19876,7 @@
       <c r="BS18" s="18"/>
       <c r="BT18" s="18"/>
     </row>
-    <row r="19" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B19" s="30" t="s">
         <v>107</v>
       </c>
@@ -20003,7 +20019,7 @@
       <c r="BS19" s="18"/>
       <c r="BT19" s="18"/>
     </row>
-    <row r="20" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B20" s="30" t="str">
         <f>'[1]Table data (2)'!A16</f>
         <v>Large scale solar PV</v>
@@ -20153,7 +20169,7 @@
       <c r="BS20" s="18"/>
       <c r="BT20" s="18"/>
     </row>
-    <row r="21" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B21" s="30" t="str">
         <f>'[1]Table data (2)'!A18</f>
         <v>Wind onshore</v>
@@ -20297,7 +20313,7 @@
       <c r="BS21" s="18"/>
       <c r="BT21" s="18"/>
     </row>
-    <row r="22" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B22" s="30" t="str">
         <f>'[1]Table data (2)'!A19</f>
         <v>Wind offshore</v>
@@ -20441,7 +20457,7 @@
       <c r="BS22" s="18"/>
       <c r="BT22" s="18"/>
     </row>
-    <row r="23" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B23" s="30">
         <f>'[1]Table data (2)'!A20</f>
         <v>2030</v>
@@ -20505,7 +20521,7 @@
       <c r="BS23" s="18"/>
       <c r="BT23" s="18"/>
     </row>
-    <row r="24" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B24" s="30" t="str">
         <f>'[1]Table data (2)'!A21</f>
         <v>Gas with CCS</v>
@@ -20632,7 +20648,7 @@
       <c r="BS24" s="18"/>
       <c r="BT24" s="18"/>
     </row>
-    <row r="25" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B25" s="30" t="str">
         <f>'[1]Table data (2)'!A22</f>
         <v>Gas combined cycle</v>
@@ -20760,7 +20776,7 @@
       <c r="BS25" s="18"/>
       <c r="BT25" s="18"/>
     </row>
-    <row r="26" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B26" s="30" t="str">
         <f>'[1]Table data (2)'!A23</f>
         <v>Gas open cycle (small)</v>
@@ -20887,7 +20903,7 @@
       <c r="BS26" s="18"/>
       <c r="BT26" s="18"/>
     </row>
-    <row r="27" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B27" s="30" t="str">
         <f>'[1]Table data (2)'!A24</f>
         <v>Gas open cycle (large)</v>
@@ -20998,7 +21014,7 @@
       <c r="BS27" s="18"/>
       <c r="BT27" s="18"/>
     </row>
-    <row r="28" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B28" s="30" t="str">
         <f>'[1]Table data (2)'!A25</f>
         <v>Gas reciprocating</v>
@@ -21108,7 +21124,7 @@
       <c r="BS28" s="18"/>
       <c r="BT28" s="18"/>
     </row>
-    <row r="29" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B29" s="30" t="str">
         <f>'[1]Table data (2)'!A26</f>
         <v>Hydrogen reciprocating</v>
@@ -21220,7 +21236,7 @@
       <c r="BS29" s="18"/>
       <c r="BT29" s="18"/>
     </row>
-    <row r="30" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B30" s="30" t="str">
         <f>'[1]Table data (2)'!A27</f>
         <v>Black coal with CCS</v>
@@ -21332,7 +21348,7 @@
       <c r="BS30" s="18"/>
       <c r="BT30" s="18"/>
     </row>
-    <row r="31" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B31" s="30" t="str">
         <f>'[1]Table data (2)'!A28</f>
         <v>Black coal</v>
@@ -21431,7 +21447,7 @@
       <c r="BE31" s="18"/>
       <c r="BF31" s="18"/>
     </row>
-    <row r="32" spans="2:72" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B32" s="30" t="str">
         <f>'[1]Table data (2)'!A29</f>
         <v>Brown coal</v>
@@ -21530,7 +21546,7 @@
       <c r="BE32" s="18"/>
       <c r="BF32" s="18"/>
     </row>
-    <row r="33" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B33" s="30" t="s">
         <v>105</v>
       </c>
@@ -21628,7 +21644,7 @@
       <c r="BE33" s="18"/>
       <c r="BF33" s="18"/>
     </row>
-    <row r="34" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B34" s="30" t="s">
         <v>106</v>
       </c>
@@ -21726,7 +21742,7 @@
       <c r="BE34" s="18"/>
       <c r="BF34" s="18"/>
     </row>
-    <row r="35" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B35" s="30" t="s">
         <v>107</v>
       </c>
@@ -21824,7 +21840,7 @@
       <c r="BE35" s="18"/>
       <c r="BF35" s="18"/>
     </row>
-    <row r="36" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B36" s="30" t="str">
         <f>'[1]Table data (2)'!A32</f>
         <v>Large scale solar PV</v>
@@ -21923,7 +21939,7 @@
       <c r="BE36" s="18"/>
       <c r="BF36" s="18"/>
     </row>
-    <row r="37" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B37" s="30" t="str">
         <f>'[1]Table data (2)'!A34</f>
         <v>Wind onshore</v>
@@ -22021,7 +22037,7 @@
       <c r="BE37" s="18"/>
       <c r="BF37" s="18"/>
     </row>
-    <row r="38" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B38" s="30" t="str">
         <f>'[1]Table data (2)'!A35</f>
         <v>Wind offshore</v>
@@ -22118,7 +22134,7 @@
       <c r="BE38" s="18"/>
       <c r="BF38" s="18"/>
     </row>
-    <row r="39" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B39" s="30">
         <f>'[1]Table data (2)'!A36</f>
         <v>2040</v>
@@ -22151,7 +22167,7 @@
       <c r="BE39" s="18"/>
       <c r="BF39" s="18"/>
     </row>
-    <row r="40" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B40" s="30" t="str">
         <f>'[1]Table data (2)'!A37</f>
         <v>Gas with CCS</v>
@@ -22249,7 +22265,7 @@
       <c r="BE40" s="18"/>
       <c r="BF40" s="18"/>
     </row>
-    <row r="41" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B41" s="30" t="str">
         <f>'[1]Table data (2)'!A38</f>
         <v>Gas combined cycle</v>
@@ -22348,7 +22364,7 @@
       <c r="BE41" s="18"/>
       <c r="BF41" s="18"/>
     </row>
-    <row r="42" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B42" s="30" t="str">
         <f>'[1]Table data (2)'!A39</f>
         <v>Gas open cycle (small)</v>
@@ -22445,7 +22461,7 @@
       <c r="BE42" s="18"/>
       <c r="BF42" s="18"/>
     </row>
-    <row r="43" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B43" s="30" t="str">
         <f>'[1]Table data (2)'!A40</f>
         <v>Gas open cycle (large)</v>
@@ -22541,7 +22557,7 @@
       <c r="BE43" s="18"/>
       <c r="BF43" s="18"/>
     </row>
-    <row r="44" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B44" s="30" t="str">
         <f>'[1]Table data (2)'!A41</f>
         <v>Gas reciprocating</v>
@@ -22637,7 +22653,7 @@
       <c r="BE44" s="18"/>
       <c r="BF44" s="18"/>
     </row>
-    <row r="45" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B45" s="30" t="str">
         <f>'[1]Table data (2)'!A42</f>
         <v>Hydrogen reciprocating</v>
@@ -22735,7 +22751,7 @@
       <c r="BE45" s="18"/>
       <c r="BF45" s="18"/>
     </row>
-    <row r="46" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B46" s="30" t="str">
         <f>'[1]Table data (2)'!A43</f>
         <v>Black coal with CCS</v>
@@ -22832,7 +22848,7 @@
       <c r="BE46" s="18"/>
       <c r="BF46" s="18"/>
     </row>
-    <row r="47" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B47" s="30" t="str">
         <f>'[1]Table data (2)'!A44</f>
         <v>Black coal</v>
@@ -22929,7 +22945,7 @@
       <c r="BE47" s="18"/>
       <c r="BF47" s="18"/>
     </row>
-    <row r="48" spans="2:58" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:58" x14ac:dyDescent="0.25">
       <c r="B48" s="30" t="str">
         <f>'[1]Table data (2)'!A45</f>
         <v>Brown coal</v>
@@ -23024,7 +23040,7 @@
       <c r="BE48" s="18"/>
       <c r="BF48" s="18"/>
     </row>
-    <row r="49" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B49" s="30" t="s">
         <v>105</v>
       </c>
@@ -23110,7 +23126,7 @@
       </c>
       <c r="AH49" s="18"/>
     </row>
-    <row r="50" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B50" s="30" t="s">
         <v>106</v>
       </c>
@@ -23196,7 +23212,7 @@
       </c>
       <c r="AH50" s="18"/>
     </row>
-    <row r="51" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B51" s="30" t="s">
         <v>107</v>
       </c>
@@ -23282,7 +23298,7 @@
       </c>
       <c r="AH51" s="18"/>
     </row>
-    <row r="52" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B52" s="30" t="str">
         <f>'[1]Table data (2)'!A48</f>
         <v>Large scale solar PV</v>
@@ -23369,7 +23385,7 @@
       </c>
       <c r="AH52" s="18"/>
     </row>
-    <row r="53" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B53" s="30" t="str">
         <f>'[1]Table data (2)'!A50</f>
         <v>Wind onshore</v>
@@ -23456,7 +23472,7 @@
       </c>
       <c r="AH53" s="18"/>
     </row>
-    <row r="54" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B54" s="30" t="str">
         <f>'[1]Table data (2)'!A51</f>
         <v>Wind offshore</v>
@@ -23541,7 +23557,7 @@
       </c>
       <c r="AH54" s="18"/>
     </row>
-    <row r="55" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B55" s="30">
         <f>'[1]Table data (2)'!A52</f>
         <v>2050</v>
@@ -23562,7 +23578,7 @@
       <c r="AF55" s="18"/>
       <c r="AH55" s="18"/>
     </row>
-    <row r="56" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B56" s="30" t="str">
         <f>'[1]Table data (2)'!A53</f>
         <v>Gas with CCS</v>
@@ -23648,7 +23664,7 @@
         <v>252.00844499215879</v>
       </c>
     </row>
-    <row r="57" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B57" s="30" t="str">
         <f>'[1]Table data (2)'!A54</f>
         <v>Gas combined cycle</v>
@@ -23735,7 +23751,7 @@
       </c>
       <c r="AH57" s="18"/>
     </row>
-    <row r="58" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B58" s="30" t="str">
         <f>'[1]Table data (2)'!A55</f>
         <v>Gas open cycle (small)</v>
@@ -23822,7 +23838,7 @@
       </c>
       <c r="AH58" s="18"/>
     </row>
-    <row r="59" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B59" s="30" t="str">
         <f>'[1]Table data (2)'!A56</f>
         <v>Gas open cycle (large)</v>
@@ -23908,7 +23924,7 @@
       </c>
       <c r="AH59" s="18"/>
     </row>
-    <row r="60" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B60" s="30" t="str">
         <f>'[1]Table data (2)'!A57</f>
         <v>Gas reciprocating</v>
@@ -23994,7 +24010,7 @@
         <v>281.41833824733158</v>
       </c>
     </row>
-    <row r="61" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B61" s="30" t="str">
         <f>'[1]Table data (2)'!A58</f>
         <v>Hydrogen reciprocating</v>
@@ -24081,7 +24097,7 @@
       <c r="AH61" s="18"/>
       <c r="AI61" s="18"/>
     </row>
-    <row r="62" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B62" s="30" t="str">
         <f>'[1]Table data (2)'!A59</f>
         <v>Black coal with CCS</v>
@@ -24169,7 +24185,7 @@
       <c r="AH62" s="18"/>
       <c r="AI62" s="18"/>
     </row>
-    <row r="63" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B63" s="30" t="str">
         <f>'[1]Table data (2)'!A60</f>
         <v>Black coal</v>
@@ -24257,7 +24273,7 @@
       <c r="AH63" s="18"/>
       <c r="AI63" s="18"/>
     </row>
-    <row r="64" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B64" s="30" t="str">
         <f>'[1]Table data (2)'!A61</f>
         <v>Brown coal</v>
@@ -24345,7 +24361,7 @@
       <c r="AH64" s="18"/>
       <c r="AI64" s="18"/>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B65" s="30" t="s">
         <v>105</v>
       </c>
@@ -24432,7 +24448,7 @@
       <c r="AH65" s="18"/>
       <c r="AI65" s="18"/>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B66" s="30" t="s">
         <v>106</v>
       </c>
@@ -24519,7 +24535,7 @@
       <c r="AH66" s="18"/>
       <c r="AI66" s="18"/>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B67" s="30" t="s">
         <v>107</v>
       </c>
@@ -24606,7 +24622,7 @@
       <c r="AH67" s="18"/>
       <c r="AI67" s="18"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B68" s="30" t="str">
         <f>'[1]Table data (2)'!A64</f>
         <v>Large scale solar PV</v>
@@ -24694,7 +24710,7 @@
       <c r="AH68" s="18"/>
       <c r="AI68" s="18"/>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B69" s="30" t="str">
         <f>'[1]Table data (2)'!A66</f>
         <v>Wind onshore</v>
@@ -24781,7 +24797,7 @@
       <c r="AH69" s="18"/>
       <c r="AI69" s="18"/>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B70" s="30" t="str">
         <f>'[1]Table data (2)'!A67</f>
         <v>Wind offshore</v>
@@ -24866,11 +24882,11 @@
       <c r="AH70" s="18"/>
       <c r="AI70" s="18"/>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.25">
       <c r="AH71" s="18"/>
       <c r="AI71" s="18"/>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B75" s="31"/>
       <c r="C75" s="31"/>
       <c r="D75" s="31"/>
@@ -24887,7 +24903,7 @@
       <c r="O75" s="31"/>
       <c r="P75" s="31"/>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B76" s="31"/>
       <c r="C76" s="31"/>
       <c r="D76" s="31"/>
@@ -24904,7 +24920,7 @@
       <c r="O76" s="31"/>
       <c r="P76" s="31"/>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
       <c r="D77" s="31"/>
@@ -24921,7 +24937,7 @@
       <c r="O77" s="31"/>
       <c r="P77" s="31"/>
     </row>
-    <row r="78" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
@@ -24938,7 +24954,7 @@
       <c r="O78" s="31"/>
       <c r="P78" s="31"/>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
@@ -24955,7 +24971,7 @@
       <c r="O79" s="31"/>
       <c r="P79" s="31"/>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
@@ -24991,35 +25007,35 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17504738-8A2D-49F0-AD64-D2140E6DC2FB}">
   <dimension ref="C2:K37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="9" max="9" width="5.453125" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C4" s="8"/>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="74"/>
+      <c r="E4" s="75"/>
       <c r="F4" s="61"/>
-      <c r="G4" s="74" t="s">
+      <c r="G4" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="61"/>
-      <c r="J4" s="74" t="s">
+      <c r="J4" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="74"/>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="K4" s="75"/>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" s="7"/>
       <c r="D5" s="23" t="s">
         <v>65</v>
@@ -25027,22 +25043,22 @@
       <c r="E5" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="75"/>
+      <c r="G5" s="77"/>
       <c r="H5" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="75" t="s">
+      <c r="I5" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="75"/>
+      <c r="J5" s="77"/>
       <c r="K5" s="23" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" s="34">
         <v>2024</v>
       </c>
@@ -25067,7 +25083,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" s="35">
         <v>2025</v>
       </c>
@@ -25077,22 +25093,22 @@
       <c r="E7" s="23">
         <v>2756</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="77">
         <v>2482</v>
       </c>
-      <c r="G7" s="75"/>
+      <c r="G7" s="77"/>
       <c r="H7" s="23">
         <v>2605</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="77">
         <v>2513</v>
       </c>
-      <c r="J7" s="75"/>
+      <c r="J7" s="77"/>
       <c r="K7" s="23">
         <v>2638</v>
       </c>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" s="34">
         <v>2026</v>
       </c>
@@ -25117,7 +25133,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" s="35">
         <v>2027</v>
       </c>
@@ -25127,22 +25143,22 @@
       <c r="E9" s="23">
         <v>2596</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="77">
         <v>2087</v>
       </c>
-      <c r="G9" s="75"/>
+      <c r="G9" s="77"/>
       <c r="H9" s="23">
         <v>2190</v>
       </c>
-      <c r="I9" s="75">
+      <c r="I9" s="77">
         <v>2167</v>
       </c>
-      <c r="J9" s="75"/>
+      <c r="J9" s="77"/>
       <c r="K9" s="23">
         <v>2274</v>
       </c>
     </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C10" s="34">
         <v>2028</v>
       </c>
@@ -25167,7 +25183,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C11" s="35">
         <v>2029</v>
       </c>
@@ -25177,22 +25193,22 @@
       <c r="E11" s="23">
         <v>2444</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="77">
         <v>1755</v>
       </c>
-      <c r="G11" s="75"/>
+      <c r="G11" s="77"/>
       <c r="H11" s="23">
         <v>1842</v>
       </c>
-      <c r="I11" s="75">
+      <c r="I11" s="77">
         <v>1868</v>
       </c>
-      <c r="J11" s="75"/>
+      <c r="J11" s="77"/>
       <c r="K11" s="23">
         <v>1961</v>
       </c>
     </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C12" s="34">
         <v>2030</v>
       </c>
@@ -25217,7 +25233,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C13" s="35">
         <v>2031</v>
       </c>
@@ -25227,22 +25243,22 @@
       <c r="E13" s="23">
         <v>2302</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="77">
         <v>1476</v>
       </c>
-      <c r="G13" s="75"/>
+      <c r="G13" s="77"/>
       <c r="H13" s="23">
         <v>1549</v>
       </c>
-      <c r="I13" s="75">
+      <c r="I13" s="77">
         <v>1611</v>
       </c>
-      <c r="J13" s="75"/>
+      <c r="J13" s="77"/>
       <c r="K13" s="23">
         <v>1691</v>
       </c>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C14" s="34">
         <v>2032</v>
       </c>
@@ -25267,7 +25283,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C15" s="35">
         <v>2033</v>
       </c>
@@ -25277,22 +25293,22 @@
       <c r="E15" s="23">
         <v>2168</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="77">
         <v>1241</v>
       </c>
-      <c r="G15" s="75"/>
+      <c r="G15" s="77"/>
       <c r="H15" s="23">
         <v>1303</v>
       </c>
-      <c r="I15" s="75">
+      <c r="I15" s="77">
         <v>1389</v>
       </c>
-      <c r="J15" s="75"/>
+      <c r="J15" s="77"/>
       <c r="K15" s="23">
         <v>1458</v>
       </c>
     </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C16" s="34">
         <v>2034</v>
       </c>
@@ -25317,7 +25333,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C17" s="35">
         <v>2035</v>
       </c>
@@ -25327,22 +25343,22 @@
       <c r="E17" s="23">
         <v>2041</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="77">
         <v>1063</v>
       </c>
-      <c r="G17" s="75"/>
+      <c r="G17" s="77"/>
       <c r="H17" s="23">
         <v>1116</v>
       </c>
-      <c r="I17" s="75">
+      <c r="I17" s="77">
         <v>1221</v>
       </c>
-      <c r="J17" s="75"/>
+      <c r="J17" s="77"/>
       <c r="K17" s="23">
         <v>1281</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C18" s="34">
         <v>2036</v>
       </c>
@@ -25367,7 +25383,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C19" s="35">
         <v>2037</v>
       </c>
@@ -25377,22 +25393,22 @@
       <c r="E19" s="23">
         <v>1922</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="77">
         <v>944</v>
       </c>
-      <c r="G19" s="75"/>
+      <c r="G19" s="77"/>
       <c r="H19" s="23">
         <v>991</v>
       </c>
-      <c r="I19" s="75">
+      <c r="I19" s="77">
         <v>1207</v>
       </c>
-      <c r="J19" s="75"/>
+      <c r="J19" s="77"/>
       <c r="K19" s="23">
         <v>1267</v>
       </c>
     </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C20" s="34">
         <v>2038</v>
       </c>
@@ -25417,7 +25433,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C21" s="35">
         <v>2039</v>
       </c>
@@ -25427,22 +25443,22 @@
       <c r="E21" s="23">
         <v>1810</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="77">
         <v>913</v>
       </c>
-      <c r="G21" s="75"/>
+      <c r="G21" s="77"/>
       <c r="H21" s="23">
         <v>958</v>
       </c>
-      <c r="I21" s="75">
+      <c r="I21" s="77">
         <v>1143</v>
       </c>
-      <c r="J21" s="75"/>
+      <c r="J21" s="77"/>
       <c r="K21" s="23">
         <v>1199</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C22" s="34">
         <v>2040</v>
       </c>
@@ -25467,7 +25483,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C23" s="35">
         <v>2041</v>
       </c>
@@ -25477,22 +25493,22 @@
       <c r="E23" s="23">
         <v>1763</v>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="77">
         <v>888</v>
       </c>
-      <c r="G23" s="75"/>
+      <c r="G23" s="77"/>
       <c r="H23" s="23">
         <v>932</v>
       </c>
-      <c r="I23" s="75">
+      <c r="I23" s="77">
         <v>1110</v>
       </c>
-      <c r="J23" s="75"/>
+      <c r="J23" s="77"/>
       <c r="K23" s="23">
         <v>1165</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C24" s="34">
         <v>2042</v>
       </c>
@@ -25517,7 +25533,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="35">
         <v>2043</v>
       </c>
@@ -25527,22 +25543,22 @@
       <c r="E25" s="23">
         <v>1741</v>
       </c>
-      <c r="F25" s="75">
+      <c r="F25" s="77">
         <v>844</v>
       </c>
-      <c r="G25" s="75"/>
+      <c r="G25" s="77"/>
       <c r="H25" s="23">
         <v>886</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="77">
         <v>1074</v>
       </c>
-      <c r="J25" s="75"/>
+      <c r="J25" s="77"/>
       <c r="K25" s="23">
         <v>1127</v>
       </c>
     </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C26" s="34">
         <v>2044</v>
       </c>
@@ -25567,7 +25583,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C27" s="35">
         <v>2045</v>
       </c>
@@ -25577,22 +25593,22 @@
       <c r="E27" s="23">
         <v>1726</v>
       </c>
-      <c r="F27" s="75">
+      <c r="F27" s="77">
         <v>814</v>
       </c>
-      <c r="G27" s="75"/>
+      <c r="G27" s="77"/>
       <c r="H27" s="23">
         <v>855</v>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="77">
         <v>1055</v>
       </c>
-      <c r="J27" s="75"/>
+      <c r="J27" s="77"/>
       <c r="K27" s="23">
         <v>1108</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C28" s="34">
         <v>2046</v>
       </c>
@@ -25617,7 +25633,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C29" s="35">
         <v>2047</v>
       </c>
@@ -25627,22 +25643,22 @@
       <c r="E29" s="23">
         <v>1671</v>
       </c>
-      <c r="F29" s="75">
+      <c r="F29" s="77">
         <v>764</v>
       </c>
-      <c r="G29" s="75"/>
+      <c r="G29" s="77"/>
       <c r="H29" s="23">
         <v>802</v>
       </c>
-      <c r="I29" s="75">
+      <c r="I29" s="77">
         <v>1043</v>
       </c>
-      <c r="J29" s="75"/>
+      <c r="J29" s="77"/>
       <c r="K29" s="23">
         <v>1095</v>
       </c>
     </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C30" s="34">
         <v>2048</v>
       </c>
@@ -25667,7 +25683,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C31" s="35">
         <v>2049</v>
       </c>
@@ -25677,22 +25693,22 @@
       <c r="E31" s="23">
         <v>1609</v>
       </c>
-      <c r="F31" s="75">
+      <c r="F31" s="77">
         <v>731</v>
       </c>
-      <c r="G31" s="75"/>
+      <c r="G31" s="77"/>
       <c r="H31" s="23">
         <v>768</v>
       </c>
-      <c r="I31" s="75">
+      <c r="I31" s="77">
         <v>1039</v>
       </c>
-      <c r="J31" s="75"/>
+      <c r="J31" s="77"/>
       <c r="K31" s="23">
         <v>1091</v>
       </c>
     </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C32" s="34">
         <v>2050</v>
       </c>
@@ -25717,7 +25733,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C33" s="35">
         <v>2051</v>
       </c>
@@ -25727,22 +25743,22 @@
       <c r="E33" s="23">
         <v>1595</v>
       </c>
-      <c r="F33" s="75">
+      <c r="F33" s="77">
         <v>725</v>
       </c>
-      <c r="G33" s="75"/>
+      <c r="G33" s="77"/>
       <c r="H33" s="23">
         <v>761</v>
       </c>
-      <c r="I33" s="75">
+      <c r="I33" s="77">
         <v>1038</v>
       </c>
-      <c r="J33" s="75"/>
+      <c r="J33" s="77"/>
       <c r="K33" s="23">
         <v>1089</v>
       </c>
     </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C34" s="34">
         <v>2052</v>
       </c>
@@ -25767,7 +25783,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C35" s="35">
         <v>2053</v>
       </c>
@@ -25777,22 +25793,22 @@
       <c r="E35" s="23">
         <v>1596</v>
       </c>
-      <c r="F35" s="75">
+      <c r="F35" s="77">
         <v>721</v>
       </c>
-      <c r="G35" s="75"/>
+      <c r="G35" s="77"/>
       <c r="H35" s="23">
         <v>756</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="77">
         <v>1038</v>
       </c>
-      <c r="J35" s="75"/>
+      <c r="J35" s="77"/>
       <c r="K35" s="23">
         <v>1090</v>
       </c>
     </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C36" s="34">
         <v>2054</v>
       </c>
@@ -25817,7 +25833,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="37" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C37" s="60">
         <v>2055</v>
       </c>
@@ -25827,23 +25843,76 @@
       <c r="E37" s="46">
         <v>1601</v>
       </c>
-      <c r="F37" s="77">
+      <c r="F37" s="74">
         <v>710</v>
       </c>
-      <c r="G37" s="77"/>
+      <c r="G37" s="74"/>
       <c r="H37" s="46">
         <v>746</v>
       </c>
-      <c r="I37" s="77">
+      <c r="I37" s="74">
         <v>1042</v>
       </c>
-      <c r="J37" s="77"/>
+      <c r="J37" s="74"/>
       <c r="K37" s="46">
         <v>1094</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="G4:H4"/>
@@ -25860,59 +25929,6 @@
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
